--- a/Assets/Resources/Data/Excels/LevelData.xlsx
+++ b/Assets/Resources/Data/Excels/LevelData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\My project\Assets\Resources\Data\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\Resources\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7314E22-6B8C-488F-8A6C-B857572B1E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE771BD1-1B9B-420B-AF5A-D191211230BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42450" yWindow="3750" windowWidth="31935" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -224,6 +224,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2669,7 +2672,7 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="16">
         <v>-1</v>
       </c>
       <c r="C101" s="11">
